--- a/output/laminas_comunales/comunal_s_isapre_a_2023_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2023_la_araucania.xlsx
@@ -384,82 +384,82 @@
         </is>
       </c>
       <c r="C2">
-        <v>41147</v>
+        <v>13.57561160692192</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="C3">
-        <v>5013</v>
+        <v>7.965901639344263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="C4">
-        <v>3520</v>
+        <v>6.621842967346508</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C5">
-        <v>3037</v>
+        <v>5.964888497254796</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C6">
-        <v>2688</v>
+        <v>4.872371379447163</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="C7">
-        <v>1842</v>
+        <v>3.87615447193377</v>
       </c>
     </row>
     <row r="8">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>1704</v>
+        <v>3.82474411923146</v>
       </c>
     </row>
     <row r="9">
@@ -489,322 +489,322 @@
         </is>
       </c>
       <c r="C9">
-        <v>1240</v>
+        <v>3.626473254759746</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="C10">
-        <v>1036</v>
+        <v>3.587295585594101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C11">
-        <v>929</v>
+        <v>3.532268170426065</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="C12">
-        <v>810</v>
+        <v>3.522132317943836</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="C13">
-        <v>806</v>
+        <v>3.242304352021615</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Purén</t>
         </is>
       </c>
       <c r="C14">
-        <v>792</v>
+        <v>2.913453299057412</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="C15">
-        <v>759</v>
+        <v>2.907228394171115</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="C16">
-        <v>754</v>
+        <v>2.84244721169464</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C17">
-        <v>572</v>
+        <v>2.808311467271825</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="C18">
-        <v>493</v>
+        <v>2.771753115465206</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="C19">
-        <v>451</v>
+        <v>2.769290775531431</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="C20">
-        <v>426</v>
+        <v>2.516491570974835</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="C21">
-        <v>408</v>
+        <v>2.499663662047626</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="C22">
-        <v>335</v>
+        <v>2.349159248269041</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="C23">
-        <v>315</v>
+        <v>2.337933323848817</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Melipeuco</t>
         </is>
       </c>
       <c r="C24">
-        <v>309</v>
+        <v>2.260467505779604</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="C25">
-        <v>286</v>
+        <v>2.103327817613532</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="C26">
-        <v>246</v>
+        <v>1.98974358974359</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Teodoro Schmidt</t>
         </is>
       </c>
       <c r="C27">
-        <v>212</v>
+        <v>1.915270710651192</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="C28">
-        <v>194</v>
+        <v>1.900079723624768</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="C29">
-        <v>190</v>
+        <v>1.772281014917761</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Cholchol</t>
         </is>
       </c>
       <c r="C30">
-        <v>176</v>
+        <v>1.721845033946945</v>
       </c>
     </row>
     <row r="31">
@@ -819,22 +819,22 @@
         </is>
       </c>
       <c r="C31">
-        <v>145</v>
+        <v>1.559139784946237</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="C32">
-        <v>139</v>
+        <v>1.488659504248297</v>
       </c>
     </row>
     <row r="33">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>87</v>
+        <v>0.9358864027538726</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +905,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
